--- a/etf_holdings/2026-10-14_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:24</t>
+          <t>2026-10-14 00:27:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:25</t>
+          <t>2026-10-14 00:27:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:27</t>
+          <t>2026-10-14 00:27:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:28</t>
+          <t>2026-10-14 00:27:12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:28</t>
+          <t>2026-10-14 00:27:12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:28</t>
+          <t>2026-10-14 00:27:12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:28</t>
+          <t>2026-10-14 00:27:12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:28</t>
+          <t>2026-10-14 00:27:12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:08</t>
+          <t>2026-10-14 01:01:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:10</t>
+          <t>2026-10-14 01:01:32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:11</t>
+          <t>2026-10-14 01:01:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:12</t>
+          <t>2026-10-14 01:01:34</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:12</t>
+          <t>2026-10-14 01:01:34</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:12</t>
+          <t>2026-10-14 01:01:34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:12</t>
+          <t>2026-10-14 01:01:34</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:12</t>
+          <t>2026-10-14 01:01:34</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.97%2490</t>
+          <t>0%2490</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.28%830,000</t>
+          <t>9.25%830,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.28%</t>
+          <t>9.25%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-5.98%1180</t>
+          <t>+0.42%1185</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.98%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.81%1,097,000</t>
+          <t>5.82%1,097,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.81%</t>
+          <t>5.82%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-9.84%5545</t>
+          <t>-0.45%5520</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.84%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5545</v>
+        <v>5520</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.60%225,000</t>
+          <t>5.56%225,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.60%</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.1%3280</t>
+          <t>+1.07%3315</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3280</v>
+        <v>3315</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.52%375,000</t>
+          <t>5.56%375,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.52%</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.16%4525</t>
+          <t>-1.1%4475</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4525</v>
+        <v>4475</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.46%269,000</t>
+          <t>5.39%269,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.46%</t>
+          <t>5.39%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,33 +814,33 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.06%8095</t>
+          <t>+1.85%8245</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8095</v>
+        <v>8245</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.20%143,000</t>
+          <t>4.72%128,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.20%</t>
+          <t>4.72%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>143000</v>
+        <v>128000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.61%1655</t>
+          <t>+4.83%1735</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.61%</t>
+          <t>+4.83%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1655</v>
+        <v>1735</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.00%539,000</t>
+          <t>4.18%539,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.52%2195</t>
+          <t>+1.14%7070</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2195</v>
+        <v>7070</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.82%387,644</t>
+          <t>3.67%116,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>387644</v>
+        <v>116000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.37%6990</t>
+          <t>-3.64%2115</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6990</v>
+        <v>2115</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.64%116,000</t>
+          <t>3.67%387,644</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>116000</v>
+        <v>387644</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.89%740</t>
+          <t>+0.95%747</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.16%952,000</t>
+          <t>3.18%952,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.18%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0%1440</t>
+          <t>-0.69%1430</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.12%483,000</t>
+          <t>3.09%483,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.1%5940</t>
+          <t>-0.93%5885</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5940</v>
+        <v>5885</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.04%114,000</t>
+          <t>3.00%114,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.03%2260</t>
+          <t>-1.11%2235</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.03%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2260</v>
+        <v>2235</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.82%278,000</t>
+          <t>2.78%278,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-6.58%1775</t>
+          <t>+0.56%1785</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.58%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1775</v>
+        <v>1785</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.57%323,000</t>
+          <t>2.58%323,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:29</t>
+          <t>2026-10-14 21:56:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.29%1715</t>
+          <t>+4.67%627</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+4.67%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1715</v>
+        <v>627</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.49%324,000</t>
+          <t>2.51%895,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.51%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>324000</v>
+        <v>895000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.82%599</t>
+          <t>+0.49%2050</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.82%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>599</v>
+        <v>2050</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.41%895,000</t>
+          <t>2.20%240,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>895000</v>
+        <v>240000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-4.23%2040</t>
+          <t>-0.55%10005</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2040</v>
+        <v>10005</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.20%240,000</t>
+          <t>1.79%40,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>240000</v>
+        <v>40000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-4.48%1600</t>
+          <t>-3.75%1540</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-4.48%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1600</v>
+        <v>1540</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.83%255,000</t>
+          <t>1.76%255,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,34 +1602,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-4.91%10060</t>
+          <t>-5.43%6880</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>10060</v>
+        <v>6880</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.81%40,000</t>
+          <t>1.60%52,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>40000</v>
+        <v>52000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.68%7275</t>
+          <t>+2.54%283</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+2.54%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7275</v>
+        <v>283</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.70%52,000</t>
+          <t>1.47%1,160,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>52000</v>
+        <v>1160000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-4.17%276</t>
+          <t>+5.69%2880</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-4.17%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>276</v>
+        <v>2880</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.44%1,160,000</t>
+          <t>1.46%113,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1160000</v>
+        <v>113000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-4.24%3275</t>
+          <t>-1.53%3225</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3275</v>
+        <v>3225</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.40%95,000</t>
+          <t>1.37%95,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-9.92%2725</t>
+          <t>-1.75%1685</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-9.92%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2725</v>
+        <v>1685</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.38%113,000</t>
+          <t>1.35%179,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>113000</v>
+        <v>179000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.95%17350</t>
+          <t>+7.69%1260</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+7.69%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>17350</v>
+        <v>1260</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.32%16,900</t>
+          <t>1.33%236,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>16900</v>
+        <v>236000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.64%2210</t>
+          <t>+0.86%17500</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2210</v>
+        <v>17500</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.11%112,000</t>
+          <t>1.32%16,900</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>112000</v>
+        <v>16900</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-5%950</t>
+          <t>-0.68%2195</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>950</v>
+        <v>2195</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.04%243,000</t>
+          <t>1.10%112,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>243000</v>
+        <v>112000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-6.98%2200</t>
+          <t>+9.4%349</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>+9.4%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2200</v>
+        <v>349</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.04%105,000</t>
+          <t>1.09%695,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>105000</v>
+        <v>695000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.99%552</t>
+          <t>+2.27%2250</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.99%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>552</v>
+        <v>2250</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.04%418,000</t>
+          <t>1.06%105,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>418000</v>
+        <v>105000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2615萬海</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.41%121.5</t>
+          <t>+2.72%567</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>121.5</v>
+        <v>567</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.01%1,850,000</t>
+          <t>1.06%418,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1850000</v>
+        <v>418000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:32</t>
+          <t>2026-10-14 21:56:40</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>1560中砂</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+5.28%319</t>
+          <t>-0.21%948</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+5.28%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>319</v>
+        <v>948</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.00%695,000</t>
+          <t>1.03%243,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>695000</v>
+        <v>243000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>2615萬海</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-7.4%488</t>
+          <t>+2.88%125</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>+2.88%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>488</v>
+        <v>125</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.93%426,000</t>
+          <t>1.03%1,850,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>426000</v>
+        <v>1850000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-4.92%1450</t>
+          <t>-1.54%480.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-4.92%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1450</v>
+        <v>480.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.88%135,000</t>
+          <t>0.92%426,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>135000</v>
+        <v>426000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-6.53%2360</t>
+          <t>+0.21%2365</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-6.53%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2360</v>
+        <v>2365</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3034聯詠</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+3.21%546</t>
+          <t>-2.76%1410</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+3.21%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>546</v>
+        <v>1410</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.74%302,000</t>
+          <t>0.85%135,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>302000</v>
+        <v>135000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>3034聯詠</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.32%187</t>
+          <t>+2.56%560</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>+2.56%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>187</v>
+        <v>560</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.74%878,000</t>
+          <t>0.76%302,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>878000</v>
+        <v>302000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3293鈊象</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0%797</t>
+          <t>0%187</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2653,20 +2653,20 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>797</v>
+        <v>187</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.61%171,000</t>
+          <t>0.73%878,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>171000</v>
+        <v>878000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3293鈊象</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-5.26%1170</t>
+          <t>+1.76%811</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>+1.76%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1170</v>
+        <v>811</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.59%113,000</t>
+          <t>0.62%171,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>113000</v>
+        <v>171000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.75%141.5</t>
+          <t>+0.35%142</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>141.5</v>
+        <v>142</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>3533嘉澤</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-2.22%926</t>
+          <t>+4.03%1935</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>+4.03%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>926</v>
+        <v>1935</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.32%77,000</t>
+          <t>0.47%54,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>77000</v>
+        <v>54000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2451創見</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-3.66%276</t>
+          <t>-0.32%923</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-3.66%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>276</v>
+        <v>923</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.31%252,000</t>
+          <t>0.32%77,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>252000</v>
+        <v>77000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>2451創見</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.69%1165</t>
+          <t>+0.91%278.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1165</v>
+        <v>278.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.31%59,000</t>
+          <t>0.31%252,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,11 +2971,11 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>59000</v>
+        <v>252000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,17 +3005,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5289宜鼎</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-5.56%1190</t>
+          <t>+2.15%1190</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>+2.15%</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -3023,20 +3023,20 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.30%55,294</t>
+          <t>0.31%59,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>55294</v>
+        <v>59000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-4.38%1965</t>
+          <t>0%1965</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-4.38%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.22%363</t>
+          <t>+1.24%367.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+1.24%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>363</v>
+        <v>367.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:33</t>
+          <t>2026-10-14 21:56:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2379瑞昱</t>
+          <t>5289宜鼎</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+1.61%758</t>
+          <t>-1.68%1170</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.61%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>758</v>
+        <v>1170</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.23%69,000</t>
+          <t>0.29%55,294</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>69000</v>
+        <v>55294</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:34</t>
+          <t>2026-10-14 21:56:43</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>2379瑞昱</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.4%2810</t>
+          <t>+2.64%778</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2810</v>
+        <v>778</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.23%18,000</t>
+          <t>0.24%69,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>18000</v>
+        <v>69000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:34</t>
+          <t>2026-10-14 21:56:43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5434崇越</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.34%595</t>
+          <t>+2.31%2875</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+2.31%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>595</v>
+        <v>2875</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.22%83,000</t>
+          <t>0.23%18,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>83000</v>
+        <v>18000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:34</t>
+          <t>2026-10-14 21:56:43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>5434崇越</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-7.18%161.5</t>
+          <t>+0.17%596</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-7.18%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>161.5</v>
+        <v>596</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.14%187,000</t>
+          <t>0.22%83,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>187000</v>
+        <v>83000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:34</t>
+          <t>2026-10-14 21:56:43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1590亞德客-KY</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-3.31%1170</t>
+          <t>+2.17%165</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1170</v>
+        <v>165</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.07%13,000</t>
+          <t>0.14%187,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>13000</v>
+        <v>187000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:34</t>
+          <t>2026-10-14 21:56:43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,34 +3493,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2412中華電</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.02%148</t>
+          <t>+1.28%1185</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>148</v>
+        <v>1185</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.04%64,000</t>
+          <t>0.07%13,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>64000</v>
+        <v>13000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-14_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:39</t>
+          <t>2026-10-14 22:02:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:40</t>
+          <t>2026-10-14 22:02:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:42</t>
+          <t>2026-10-14 22:02:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:43</t>
+          <t>2026-10-14 22:02:20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:43</t>
+          <t>2026-10-14 22:02:20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:43</t>
+          <t>2026-10-14 22:02:20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:43</t>
+          <t>2026-10-14 22:02:20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:43</t>
+          <t>2026-10-14 22:02:20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:16</t>
+          <t>2026-10-14 22:32:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:17</t>
+          <t>2026-10-14 22:32:42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:18</t>
+          <t>2026-10-14 22:32:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:20</t>
+          <t>2026-10-14 22:32:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:20</t>
+          <t>2026-10-14 22:32:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:20</t>
+          <t>2026-10-14 22:32:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:20</t>
+          <t>2026-10-14 22:32:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:20</t>
+          <t>2026-10-14 22:32:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
